--- a/GameData/GameData_String.xlsx
+++ b/GameData/GameData_String.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillString" sheetId="1" r:id="R95283727cf5749ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiString" sheetId="2" r:id="Rbadb92635a314ce6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillString" sheetId="1" r:id="Rebc3c6360eb6497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiString" sheetId="2" r:id="R8691b601224c44fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -449,13 +449,13 @@
         <x:v>DEF_Taunt_Desc</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>다음 검 적중 시 {0:0.#}초간 적을 끌어들입니다. 받는 피해 감소와 반사 강화가 적용됩니다.</x:v>
+        <x:v>{0:0.#}초 안에 적중한 다음 공격이 적을 {1:0.#}초간 도발하며, 받는 피해 감소·반사 강화가 적용됩니다. 대기 중 무기는 주황색. 쿨타임 {2:0.#}초.</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
-        <x:v>Your next sword hit forces the enemy toward you for {0:0.#}s and grants damage reduction and stronger reflection.</x:v>
+        <x:v>Your next hit within {0:0.#}s taunts for {1:0.#}s, reducing incoming damage and increasing reflection. The weapon glows orange while ready. Cooldown: {2:0.#}s.</x:v>
       </x:c>
       <x:c r="D10" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="86" customHeight="1">
@@ -841,13 +841,13 @@
         <x:v>DEF_Bash_Desc</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>다음 공격 적중 시 {0:0.#}초간 이동·공격을 막고, 해당 시간에 적이 받는 피해를 {1:0%}로 만듭니다. 준비 상태는 {2:0.#}초 유지됩니다.</x:v>
+        <x:v>{2:0.#}초 안에 적중한 다음 공격이 적을 {0:0.#}초간 기절시키고, 기절 중 받는 피해를 {1:0.#}배로 만듭니다. 대기 중 무기는 파란색. 쿨타임 {3:0.#}초.</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>Your next hit stuns for {0:0.#}s and makes the target take {1:0%} damage during the stun. The ready effect lasts {2:0.#}s.</x:v>
+        <x:v>Your next hit within {2:0.#}s stuns for {0:0.#}s and increases damage taken to {1:0.#}x during the stun. The weapon glows blue while ready. Cooldown: {3:0.#}s.</x:v>
       </x:c>
       <x:c r="D38" s="10" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="86" customHeight="1">
